--- a/uploads/govt_plot_excels/Govt_Land_Plot_(1).xlsx
+++ b/uploads/govt_plot_excels/Govt_Land_Plot_(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maasuser\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44790C2C-835D-43F1-AE71-1F8472369035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B50AB0-F683-4EE2-951C-744F254D9BE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -954,6 +954,7 @@
     <col min="17" max="17" width="14.7109375" customWidth="1"/>
     <col min="18" max="18" width="12.28515625" customWidth="1"/>
     <col min="19" max="19" width="14.140625" customWidth="1"/>
+    <col min="25" max="25" width="35.85546875" customWidth="1"/>
     <col min="26" max="26" width="13" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="13" customWidth="1"/>
     <col min="28" max="28" width="13.5703125" customWidth="1"/>
